--- a/rules/CORE-000892/positive/01/data/unit-test-coreid-FB4301_positive.xlsx
+++ b/rules/CORE-000892/positive/01/data/unit-test-coreid-FB4301_positive.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cm.xpt" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -599,627 +600,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>DOMAIN</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>CMSEQ</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>CMTRT</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>EPOCH</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>CMSTDTC</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CMSTRF</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>CMSTRTPT</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>CMENDTC</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CMENRF</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>CMENRTPT</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Study Identifier</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Domain Abbreviation</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Unique Subject Identifier</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Sequence Number</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Reported Name of Drug, Med, or Therapy</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Epoch</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Start Date/Time of Medication</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Start Relative to Reference Period</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Start relative to Reference Time Point</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>End Date/Time of Medication</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>End Relative to Reference Period</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>End relative to Reference Time Point</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="M4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>CDISC001</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>ASPIRIN</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>151</v>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CDISC001</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>ASPIRIN</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>BEFORE</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>CDISC001</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>ASPIRIN</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>VISIT 0</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>2013-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>CDISC002</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>METAMUCIL</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>2012-03</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>AFTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>CDISC002</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>METAMUCIL</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>BEFORE</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>BEFORE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>CDISC002</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>METAMUCIL</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>SCREENING</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>VISIT1</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>DURING</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>CDISC003</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>HYDROCORTISONE, TOPICAL</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>TREATMENT</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>2013-01-11</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n"/>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>VISIT99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>CDISC003</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>HYDROCORTISONE, TOPICAL</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>TREATMENT</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>BEFORE</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>VISIT99</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>CDISC003</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>HYDROCORTISONE, TOPICAL</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>TREATMENT</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>VISIT1</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n"/>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>VISIT99</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="H16" s="12" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Error group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Error level</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Row num</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Error value</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1232,6 +646,638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>CMSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>CMTRT</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>EPOCH</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CMSTRF</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CMSTRTPT</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CMENRF</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CMENRTPT</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Reported Name of Drug, Med, or Therapy</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Epoch</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Start Date/Time of Medication</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Start Relative to Reference Period</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Start relative to Reference Time Point</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>End Date/Time of Medication</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>End Relative to Reference Period</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>End relative to Reference Time Point</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>VISIT 0</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>VISIT1</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>DURING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE, TOPICAL</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>2013-01-11</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n"/>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE, TOPICAL</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>BEFORE</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE, TOPICAL</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>VISIT1</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n"/>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="H16" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/rules/CORE-000892/positive/01/data/unit-test-coreid-FB4301_positive.xlsx
+++ b/rules/CORE-000892/positive/01/data/unit-test-coreid-FB4301_positive.xlsx
@@ -953,6 +953,11 @@
           <t>SCREENING</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
           <t>BEFORE</t>
@@ -993,6 +998,11 @@
           <t>SCREENING</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>VISIT 0</t>
@@ -1040,6 +1050,11 @@
           <t>2012-03</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AFTER</t>
+        </is>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>AFTER</t>
@@ -1119,6 +1134,11 @@
           <t>SCREENING</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DURING</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>VISIT1</t>
@@ -1166,6 +1186,11 @@
           <t>2013-01-11</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="n"/>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1210,7 +1235,11 @@
           <t>BEFORE</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>VISIT99</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="n"/>
       <c r="L12" s="7" t="inlineStr">
         <is>
